--- a/results_hybrid/hybrid_planning_alpha_0.8.xlsx
+++ b/results_hybrid/hybrid_planning_alpha_0.8.xlsx
@@ -702,19 +702,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.39</v>
+        <v>1.13</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6659999999999999</v>
+        <v>1.286</v>
       </c>
     </row>
     <row r="13">
@@ -726,19 +726,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.49</v>
+        <v>2.62</v>
       </c>
       <c r="F13" t="n">
-        <v>0.75</v>
+        <v>2.816</v>
       </c>
     </row>
     <row r="14">
@@ -750,19 +750,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.64</v>
+        <v>1.05</v>
       </c>
       <c r="F14" t="n">
-        <v>0.876</v>
+        <v>1.174</v>
       </c>
     </row>
     <row r="15">
@@ -774,19 +774,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>P39</t>
+          <t>P44</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.862</v>
       </c>
     </row>
     <row r="16">
@@ -798,19 +798,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P41</t>
+          <t>P45</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.47</v>
+        <v>1.88</v>
       </c>
       <c r="F16" t="n">
-        <v>1.718</v>
+        <v>1.992</v>
       </c>
     </row>
     <row r="17">
@@ -818,23 +818,23 @@
         <v>1</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>P51</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.2</v>
+        <v>0.46</v>
       </c>
       <c r="F17" t="n">
-        <v>0.448</v>
+        <v>0.5680000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -842,23 +842,23 @@
         <v>1</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>P53</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="F18" t="n">
-        <v>0.742</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="19">
@@ -875,14 +875,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.36</v>
+        <v>0.74</v>
       </c>
       <c r="F19" t="n">
-        <v>0.544</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="20">
@@ -899,14 +899,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P32</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0.748</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="21">
@@ -923,14 +923,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>P35</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.2</v>
+        <v>0.63</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="22">
@@ -947,14 +947,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P36</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.13</v>
+        <v>0.89</v>
       </c>
       <c r="F22" t="n">
-        <v>1.278</v>
+        <v>1.018</v>
       </c>
     </row>
     <row r="23">
@@ -971,14 +971,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>P42</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.07</v>
+        <v>1.61</v>
       </c>
       <c r="F23" t="n">
-        <v>1.226</v>
+        <v>1.702</v>
       </c>
     </row>
     <row r="24">
@@ -995,14 +995,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P43</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.02</v>
+        <v>0.82</v>
       </c>
       <c r="F24" t="n">
-        <v>1.188</v>
+        <v>0.9359999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1019,14 +1019,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>P47</t>
+          <t>P40</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.732</v>
+        <v>0.6880000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1034,7 +1034,7 @@
         <v>1</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1043,14 +1043,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>P50</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.75</v>
+        <v>0.36</v>
       </c>
       <c r="F26" t="n">
-        <v>0.894</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="27">
@@ -1067,14 +1067,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P32</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.46</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5680000000000001</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="28">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P35</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.52</v>
+        <v>1.2</v>
       </c>
       <c r="F28" t="n">
-        <v>0.644</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="29">
@@ -1115,14 +1115,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P36</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.74</v>
+        <v>1.13</v>
       </c>
       <c r="F29" t="n">
-        <v>0.864</v>
+        <v>1.278</v>
       </c>
     </row>
     <row r="30">
@@ -1139,14 +1139,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P42</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="F30" t="n">
-        <v>1.14</v>
+        <v>1.226</v>
       </c>
     </row>
     <row r="31">
@@ -1163,14 +1163,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P43</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.63</v>
+        <v>1.02</v>
       </c>
       <c r="F31" t="n">
-        <v>0.742</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="32">
@@ -1187,14 +1187,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>P25</t>
+          <t>P47</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.89</v>
+        <v>0.58</v>
       </c>
       <c r="F32" t="n">
-        <v>1.018</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="33">
@@ -1211,14 +1211,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>P26</t>
+          <t>P50</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.61</v>
+        <v>0.75</v>
       </c>
       <c r="F33" t="n">
-        <v>1.702</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="34">
@@ -1226,23 +1226,23 @@
         <v>1</v>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>P28</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.82</v>
+        <v>0.51</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9359999999999999</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="35">
@@ -1250,23 +1250,23 @@
         <v>1</v>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>P40</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6880000000000001</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="36">
@@ -1278,19 +1278,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.13</v>
+        <v>0.49</v>
       </c>
       <c r="F36" t="n">
-        <v>1.286</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="37">
@@ -1302,19 +1302,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P39</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2.62</v>
+        <v>0.3</v>
       </c>
       <c r="F37" t="n">
-        <v>2.816</v>
+        <v>0.5720000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1326,19 +1326,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>P30</t>
+          <t>P41</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.05</v>
+        <v>1.47</v>
       </c>
       <c r="F38" t="n">
-        <v>1.174</v>
+        <v>1.718</v>
       </c>
     </row>
     <row r="39">
@@ -1350,19 +1350,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>P44</t>
+          <t>P46</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.75</v>
+        <v>0.31</v>
       </c>
       <c r="F39" t="n">
-        <v>0.862</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="40">
@@ -1374,19 +1374,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>P45</t>
+          <t>P49</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.88</v>
+        <v>0.91</v>
       </c>
       <c r="F40" t="n">
-        <v>1.992</v>
+        <v>1.126</v>
       </c>
     </row>
     <row r="41">
@@ -1394,23 +1394,23 @@
         <v>1</v>
       </c>
       <c r="B41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P52</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="F41" t="n">
-        <v>1.896</v>
+        <v>1.168</v>
       </c>
     </row>
     <row r="42">
@@ -1422,19 +1422,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.44</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="43">
@@ -1446,19 +1446,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="F43" t="n">
-        <v>0.618</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="44">
@@ -1470,19 +1470,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1.31</v>
+        <v>0.39</v>
       </c>
       <c r="F44" t="n">
-        <v>1.438</v>
+        <v>0.6659999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1494,19 +1494,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>P27</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.7</v>
+        <v>0.49</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8999999999999999</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="46">
@@ -1518,19 +1518,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>P38</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.99</v>
+        <v>0.64</v>
       </c>
       <c r="F46" t="n">
-        <v>1.266</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="47">
@@ -1542,19 +1542,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>P55</t>
+          <t>P31</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.45</v>
+        <v>0.61</v>
       </c>
       <c r="F47" t="n">
-        <v>0.63</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="48">
@@ -1562,7 +1562,7 @@
         <v>1</v>
       </c>
       <c r="B48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1571,14 +1571,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P33</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.34</v>
       </c>
       <c r="F48" t="n">
-        <v>0.866</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="49">
@@ -1586,7 +1586,7 @@
         <v>1</v>
       </c>
       <c r="B49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1595,14 +1595,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P51</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.352</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="50">
@@ -1610,7 +1610,7 @@
         <v>1</v>
       </c>
       <c r="B50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1619,14 +1619,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P53</t>
         </is>
       </c>
       <c r="E50" t="n">
         <v>0.51</v>
       </c>
       <c r="F50" t="n">
-        <v>0.71</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="51">
@@ -1638,19 +1638,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>P21</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.38</v>
+        <v>1.76</v>
       </c>
       <c r="F51" t="n">
-        <v>0.532</v>
+        <v>1.896</v>
       </c>
     </row>
     <row r="52">
@@ -1662,19 +1662,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="F52" t="n">
-        <v>0.606</v>
+        <v>0.6799999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -1686,19 +1686,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>P31</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="F53" t="n">
-        <v>0.706</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="54">
@@ -1710,19 +1710,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>P33</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.34</v>
+        <v>1.31</v>
       </c>
       <c r="F54" t="n">
-        <v>0.52</v>
+        <v>1.438</v>
       </c>
     </row>
     <row r="55">
@@ -1734,19 +1734,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>P46</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.31</v>
+        <v>0.7</v>
       </c>
       <c r="F55" t="n">
-        <v>0.55</v>
+        <v>0.8999999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -1758,19 +1758,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>P49</t>
+          <t>P38</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.91</v>
+        <v>0.99</v>
       </c>
       <c r="F56" t="n">
-        <v>1.126</v>
+        <v>1.266</v>
       </c>
     </row>
     <row r="57">
@@ -1782,19 +1782,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>P52</t>
+          <t>P55</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1.04</v>
+        <v>0.45</v>
       </c>
       <c r="F57" t="n">
-        <v>1.168</v>
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>
@@ -2092,19 +2092,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.13</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1.286</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="13">
@@ -2116,19 +2116,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.62</v>
+        <v>0.39</v>
       </c>
       <c r="F13" t="n">
-        <v>2.816</v>
+        <v>0.6659999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2140,19 +2140,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>P30</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.05</v>
+        <v>0.49</v>
       </c>
       <c r="F14" t="n">
-        <v>1.174</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="15">
@@ -2164,19 +2164,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>P44</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="F15" t="n">
-        <v>0.862</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="16">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P45</t>
+          <t>P49</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.88</v>
+        <v>0.91</v>
       </c>
       <c r="F16" t="n">
-        <v>1.992</v>
+        <v>1.126</v>
       </c>
     </row>
     <row r="17">
@@ -2208,23 +2208,23 @@
         <v>2</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P52</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.46</v>
+        <v>1.04</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5680000000000001</v>
+        <v>1.168</v>
       </c>
     </row>
     <row r="18">
@@ -2241,14 +2241,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.74</v>
+        <v>0.46</v>
       </c>
       <c r="F18" t="n">
-        <v>0.864</v>
+        <v>0.5680000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -2265,14 +2265,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0.52</v>
       </c>
       <c r="F19" t="n">
-        <v>1.14</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="20">
@@ -2289,14 +2289,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.63</v>
+        <v>0.74</v>
       </c>
       <c r="F20" t="n">
-        <v>0.742</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="21">
@@ -2313,14 +2313,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>P25</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1.018</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="22">
@@ -2337,14 +2337,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P26</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.61</v>
+        <v>0.63</v>
       </c>
       <c r="F22" t="n">
-        <v>1.702</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="23">
@@ -2361,14 +2361,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>P28</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9359999999999999</v>
+        <v>1.018</v>
       </c>
     </row>
     <row r="24">
@@ -2385,14 +2385,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P40</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.61</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6880000000000001</v>
+        <v>1.702</v>
       </c>
     </row>
     <row r="25">
@@ -2400,7 +2400,7 @@
         <v>2</v>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2409,14 +2409,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.52</v>
+        <v>0.82</v>
       </c>
       <c r="F25" t="n">
-        <v>0.644</v>
+        <v>0.9359999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -2424,7 +2424,7 @@
         <v>2</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2433,14 +2433,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P40</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.36</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.544</v>
+        <v>0.6880000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -2452,19 +2452,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>P32</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="F27" t="n">
-        <v>0.748</v>
+        <v>1.286</v>
       </c>
     </row>
     <row r="28">
@@ -2476,19 +2476,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>P35</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.2</v>
+        <v>2.62</v>
       </c>
       <c r="F28" t="n">
-        <v>1.4</v>
+        <v>2.816</v>
       </c>
     </row>
     <row r="29">
@@ -2500,19 +2500,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>P36</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="F29" t="n">
-        <v>1.278</v>
+        <v>1.174</v>
       </c>
     </row>
     <row r="30">
@@ -2524,19 +2524,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>P42</t>
+          <t>P44</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.07</v>
+        <v>0.75</v>
       </c>
       <c r="F30" t="n">
-        <v>1.226</v>
+        <v>0.862</v>
       </c>
     </row>
     <row r="31">
@@ -2548,19 +2548,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>P43</t>
+          <t>P45</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.02</v>
+        <v>1.88</v>
       </c>
       <c r="F31" t="n">
-        <v>1.188</v>
+        <v>1.992</v>
       </c>
     </row>
     <row r="32">
@@ -2568,7 +2568,7 @@
         <v>2</v>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2577,14 +2577,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>P47</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.58</v>
+        <v>0.36</v>
       </c>
       <c r="F32" t="n">
-        <v>0.732</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="33">
@@ -2592,7 +2592,7 @@
         <v>2</v>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2601,14 +2601,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>P50</t>
+          <t>P32</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.894</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="34">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P35</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="F34" t="n">
-        <v>1.896</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="35">
@@ -2644,19 +2644,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P36</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.44</v>
+        <v>1.13</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6799999999999999</v>
+        <v>1.278</v>
       </c>
     </row>
     <row r="36">
@@ -2668,19 +2668,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P42</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="F36" t="n">
-        <v>0.618</v>
+        <v>1.226</v>
       </c>
     </row>
     <row r="37">
@@ -2692,19 +2692,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P43</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.31</v>
+        <v>1.02</v>
       </c>
       <c r="F37" t="n">
-        <v>1.438</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="38">
@@ -2716,19 +2716,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>P27</t>
+          <t>P47</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8999999999999999</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="39">
@@ -2740,19 +2740,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>P38</t>
+          <t>P50</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="F39" t="n">
-        <v>1.266</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="40">
@@ -2760,23 +2760,23 @@
         <v>2</v>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>P55</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="F40" t="n">
-        <v>0.63</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="41">
@@ -2793,14 +2793,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.39</v>
+        <v>0.51</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6659999999999999</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="42">
@@ -2817,14 +2817,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.64</v>
+        <v>0.38</v>
       </c>
       <c r="F42" t="n">
-        <v>0.876</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="43">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>P31</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.61</v>
+        <v>0.49</v>
       </c>
       <c r="F43" t="n">
-        <v>0.706</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="44">
@@ -2865,14 +2865,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>P33</t>
+          <t>P31</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.34</v>
+        <v>0.61</v>
       </c>
       <c r="F44" t="n">
-        <v>0.52</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="45">
@@ -2889,14 +2889,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>P39</t>
+          <t>P33</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="46">
@@ -2913,14 +2913,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>P41</t>
+          <t>P39</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1.47</v>
+        <v>0.3</v>
       </c>
       <c r="F46" t="n">
-        <v>1.718</v>
+        <v>0.5720000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2937,14 +2937,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>P46</t>
+          <t>P41</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.31</v>
+        <v>1.47</v>
       </c>
       <c r="F47" t="n">
-        <v>0.55</v>
+        <v>1.718</v>
       </c>
     </row>
     <row r="48">
@@ -2961,14 +2961,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>P49</t>
+          <t>P46</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.91</v>
+        <v>0.31</v>
       </c>
       <c r="F48" t="n">
-        <v>1.126</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="49">
@@ -2976,7 +2976,7 @@
         <v>2</v>
       </c>
       <c r="B49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2985,14 +2985,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P51</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.866</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="50">
@@ -3000,7 +3000,7 @@
         <v>2</v>
       </c>
       <c r="B50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -3009,14 +3009,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P53</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.26</v>
+        <v>0.51</v>
       </c>
       <c r="F50" t="n">
-        <v>0.352</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="51">
@@ -3028,19 +3028,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.49</v>
+        <v>1.76</v>
       </c>
       <c r="F51" t="n">
-        <v>0.75</v>
+        <v>1.896</v>
       </c>
     </row>
     <row r="52">
@@ -3052,19 +3052,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="F52" t="n">
-        <v>0.71</v>
+        <v>0.6799999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -3076,19 +3076,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>P21</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="F53" t="n">
-        <v>0.532</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="54">
@@ -3100,19 +3100,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.49</v>
+        <v>1.31</v>
       </c>
       <c r="F54" t="n">
-        <v>0.606</v>
+        <v>1.438</v>
       </c>
     </row>
     <row r="55">
@@ -3124,19 +3124,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>P51</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="F55" t="n">
-        <v>0.448</v>
+        <v>0.8999999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -3148,19 +3148,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>P52</t>
+          <t>P38</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="F56" t="n">
-        <v>1.168</v>
+        <v>1.266</v>
       </c>
     </row>
     <row r="57">
@@ -3172,19 +3172,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>P53</t>
+          <t>P55</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="F57" t="n">
-        <v>0.742</v>
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>
@@ -3242,19 +3242,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5680000000000001</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="3">
@@ -3266,19 +3266,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.52</v>
+        <v>0.34</v>
       </c>
       <c r="F3" t="n">
-        <v>0.644</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="4">
@@ -3290,19 +3290,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.74</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="n">
-        <v>0.864</v>
+        <v>0.514</v>
       </c>
     </row>
     <row r="5">
@@ -3314,19 +3314,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="F5" t="n">
-        <v>1.14</v>
+        <v>1.082</v>
       </c>
     </row>
     <row r="6">
@@ -3338,19 +3338,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.63</v>
+        <v>0.53</v>
       </c>
       <c r="F6" t="n">
-        <v>0.742</v>
+        <v>0.7060000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -3362,19 +3362,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>P25</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="F7" t="n">
-        <v>1.018</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="8">
@@ -3386,19 +3386,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>P26</t>
+          <t>P34</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.61</v>
+        <v>0.47</v>
       </c>
       <c r="F8" t="n">
-        <v>1.702</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="9">
@@ -3410,19 +3410,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>P28</t>
+          <t>P37</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9359999999999999</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="10">
@@ -3430,7 +3430,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3439,14 +3439,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P48</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="F10" t="n">
-        <v>0.616</v>
+        <v>0.526</v>
       </c>
     </row>
     <row r="11">
@@ -3454,7 +3454,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3463,14 +3463,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P54</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.34</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.556</v>
+        <v>0.668</v>
       </c>
     </row>
     <row r="12">
@@ -3482,19 +3482,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.33</v>
+        <v>1.13</v>
       </c>
       <c r="F12" t="n">
-        <v>0.514</v>
+        <v>1.286</v>
       </c>
     </row>
     <row r="13">
@@ -3506,19 +3506,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.91</v>
+        <v>2.62</v>
       </c>
       <c r="F13" t="n">
-        <v>1.082</v>
+        <v>2.816</v>
       </c>
     </row>
     <row r="14">
@@ -3530,19 +3530,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>P23</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.53</v>
+        <v>1.05</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7060000000000001</v>
+        <v>1.174</v>
       </c>
     </row>
     <row r="15">
@@ -3554,19 +3554,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>P29</t>
+          <t>P44</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="F15" t="n">
-        <v>0.706</v>
+        <v>0.862</v>
       </c>
     </row>
     <row r="16">
@@ -3578,19 +3578,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P34</t>
+          <t>P45</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.47</v>
+        <v>1.88</v>
       </c>
       <c r="F16" t="n">
-        <v>0.634</v>
+        <v>1.992</v>
       </c>
     </row>
     <row r="17">
@@ -3598,23 +3598,23 @@
         <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>P37</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.58</v>
+        <v>1.76</v>
       </c>
       <c r="F17" t="n">
-        <v>0.78</v>
+        <v>1.896</v>
       </c>
     </row>
     <row r="18">
@@ -3622,23 +3622,23 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>P48</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="F18" t="n">
-        <v>0.526</v>
+        <v>0.6799999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -3646,23 +3646,23 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>P54</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="F19" t="n">
-        <v>0.668</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="20">
@@ -3679,14 +3679,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.76</v>
+        <v>1.31</v>
       </c>
       <c r="F20" t="n">
-        <v>1.896</v>
+        <v>1.438</v>
       </c>
     </row>
     <row r="21">
@@ -3703,14 +3703,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.8999999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3727,14 +3727,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P38</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="F22" t="n">
-        <v>0.618</v>
+        <v>1.266</v>
       </c>
     </row>
     <row r="23">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P55</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.31</v>
+        <v>0.45</v>
       </c>
       <c r="F23" t="n">
-        <v>1.438</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="24">
@@ -3766,23 +3766,23 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P27</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.7</v>
+        <v>0.46</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8999999999999999</v>
+        <v>0.5680000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -3790,23 +3790,23 @@
         <v>3</v>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>P38</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.99</v>
+        <v>0.52</v>
       </c>
       <c r="F25" t="n">
-        <v>1.266</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="26">
@@ -3814,23 +3814,23 @@
         <v>3</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>P55</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.45</v>
+        <v>0.74</v>
       </c>
       <c r="F26" t="n">
-        <v>0.63</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="27">
@@ -3847,14 +3847,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.36</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>0.544</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="28">
@@ -3871,14 +3871,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>P32</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="F28" t="n">
-        <v>0.748</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="29">
@@ -3895,14 +3895,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>P35</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.2</v>
+        <v>0.89</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4</v>
+        <v>1.018</v>
       </c>
     </row>
     <row r="30">
@@ -3919,14 +3919,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>P36</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.13</v>
+        <v>1.61</v>
       </c>
       <c r="F30" t="n">
-        <v>1.278</v>
+        <v>1.702</v>
       </c>
     </row>
     <row r="31">
@@ -3943,14 +3943,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>P40</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6880000000000001</v>
+        <v>0.9359999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -3958,7 +3958,7 @@
         <v>3</v>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3967,14 +3967,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>P42</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.07</v>
+        <v>0.36</v>
       </c>
       <c r="F32" t="n">
-        <v>1.226</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="33">
@@ -3982,7 +3982,7 @@
         <v>3</v>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3991,14 +3991,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>P43</t>
+          <t>P32</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.02</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>1.188</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="34">
@@ -4006,7 +4006,7 @@
         <v>3</v>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4015,14 +4015,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>P47</t>
+          <t>P35</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.58</v>
+        <v>1.2</v>
       </c>
       <c r="F34" t="n">
-        <v>0.732</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="35">
@@ -4030,7 +4030,7 @@
         <v>3</v>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4039,14 +4039,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>P50</t>
+          <t>P36</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="F35" t="n">
-        <v>0.894</v>
+        <v>1.278</v>
       </c>
     </row>
     <row r="36">
@@ -4058,19 +4058,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P40</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>1.286</v>
+        <v>0.6880000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -4082,19 +4082,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P42</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2.62</v>
+        <v>1.07</v>
       </c>
       <c r="F37" t="n">
-        <v>2.816</v>
+        <v>1.226</v>
       </c>
     </row>
     <row r="38">
@@ -4106,19 +4106,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>P30</t>
+          <t>P43</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="F38" t="n">
-        <v>1.174</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="39">
@@ -4130,19 +4130,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>P44</t>
+          <t>P47</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="F39" t="n">
-        <v>0.862</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="40">
@@ -4154,19 +4154,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>P45</t>
+          <t>P50</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.88</v>
+        <v>0.75</v>
       </c>
       <c r="F40" t="n">
-        <v>1.992</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="41">
@@ -4183,14 +4183,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.49</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>0.75</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="42">
@@ -4207,14 +4207,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>P21</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.38</v>
+        <v>0.26</v>
       </c>
       <c r="F42" t="n">
-        <v>0.532</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="43">
@@ -4231,14 +4231,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>0.49</v>
       </c>
       <c r="F43" t="n">
-        <v>0.606</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="44">
@@ -4255,14 +4255,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>P39</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.3</v>
+        <v>0.51</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="45">
@@ -4279,14 +4279,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>P41</t>
+          <t>P33</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.47</v>
+        <v>0.34</v>
       </c>
       <c r="F45" t="n">
-        <v>1.718</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="46">
@@ -4303,14 +4303,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>P52</t>
+          <t>P41</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="F46" t="n">
-        <v>1.168</v>
+        <v>1.718</v>
       </c>
     </row>
     <row r="47">
@@ -4327,14 +4327,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>P53</t>
+          <t>P51</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.51</v>
+        <v>0.2</v>
       </c>
       <c r="F47" t="n">
-        <v>0.742</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="48">
@@ -4342,7 +4342,7 @@
         <v>3</v>
       </c>
       <c r="B48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -4351,14 +4351,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P52</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="F48" t="n">
-        <v>0.866</v>
+        <v>1.168</v>
       </c>
     </row>
     <row r="49">
@@ -4375,14 +4375,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="F49" t="n">
-        <v>0.352</v>
+        <v>0.6659999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.39</v>
+        <v>0.64</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6659999999999999</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="51">
@@ -4423,14 +4423,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.64</v>
+        <v>0.38</v>
       </c>
       <c r="F51" t="n">
-        <v>0.876</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="52">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="F52" t="n">
-        <v>0.71</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="53">
@@ -4495,14 +4495,14 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>P33</t>
+          <t>P39</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="F54" t="n">
-        <v>0.52</v>
+        <v>0.5720000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -4567,14 +4567,14 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>P51</t>
+          <t>P53</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.2</v>
+        <v>0.51</v>
       </c>
       <c r="F57" t="n">
-        <v>0.448</v>
+        <v>0.742</v>
       </c>
     </row>
   </sheetData>
@@ -4632,19 +4632,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.76</v>
+        <v>1.13</v>
       </c>
       <c r="F2" t="n">
-        <v>1.896</v>
+        <v>1.286</v>
       </c>
     </row>
     <row r="3">
@@ -4656,19 +4656,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.44</v>
+        <v>2.62</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6799999999999999</v>
+        <v>2.816</v>
       </c>
     </row>
     <row r="4">
@@ -4680,19 +4680,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.45</v>
+        <v>1.05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.618</v>
+        <v>1.174</v>
       </c>
     </row>
     <row r="5">
@@ -4704,19 +4704,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P44</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.31</v>
+        <v>0.75</v>
       </c>
       <c r="F5" t="n">
-        <v>1.438</v>
+        <v>0.862</v>
       </c>
     </row>
     <row r="6">
@@ -4728,19 +4728,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>P27</t>
+          <t>P45</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7</v>
+        <v>1.88</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8999999999999999</v>
+        <v>1.992</v>
       </c>
     </row>
     <row r="7">
@@ -4748,23 +4748,23 @@
         <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>P38</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.99</v>
+        <v>0.46</v>
       </c>
       <c r="F7" t="n">
-        <v>1.266</v>
+        <v>0.5680000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -4772,23 +4772,23 @@
         <v>4</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>P55</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="F8" t="n">
-        <v>0.63</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="9">
@@ -4805,14 +4805,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5680000000000001</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="10">
@@ -4829,14 +4829,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.52</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.644</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="11">
@@ -4853,14 +4853,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="F11" t="n">
-        <v>0.864</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="12">
@@ -4877,14 +4877,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="F12" t="n">
-        <v>1.14</v>
+        <v>1.018</v>
       </c>
     </row>
     <row r="13">
@@ -4901,14 +4901,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.63</v>
+        <v>1.61</v>
       </c>
       <c r="F13" t="n">
-        <v>0.742</v>
+        <v>1.702</v>
       </c>
     </row>
     <row r="14">
@@ -4925,14 +4925,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>P25</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="F14" t="n">
-        <v>1.018</v>
+        <v>0.9359999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -4940,7 +4940,7 @@
         <v>4</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -4949,14 +4949,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>P26</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.61</v>
+        <v>0.36</v>
       </c>
       <c r="F15" t="n">
-        <v>1.702</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="16">
@@ -4964,7 +4964,7 @@
         <v>4</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -4973,14 +4973,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P28</t>
+          <t>P32</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9359999999999999</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="17">
@@ -4997,14 +4997,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P35</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.36</v>
+        <v>1.2</v>
       </c>
       <c r="F17" t="n">
-        <v>0.544</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="18">
@@ -5021,14 +5021,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>P32</t>
+          <t>P36</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="F18" t="n">
-        <v>0.748</v>
+        <v>1.278</v>
       </c>
     </row>
     <row r="19">
@@ -5045,14 +5045,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>P35</t>
+          <t>P40</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4</v>
+        <v>0.6880000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -5069,14 +5069,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P36</t>
+          <t>P42</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="F20" t="n">
-        <v>1.278</v>
+        <v>1.226</v>
       </c>
     </row>
     <row r="21">
@@ -5093,14 +5093,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>P40</t>
+          <t>P43</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6880000000000001</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="22">
@@ -5117,14 +5117,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P42</t>
+          <t>P47</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.07</v>
+        <v>0.58</v>
       </c>
       <c r="F22" t="n">
-        <v>1.226</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="23">
@@ -5141,14 +5141,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>P43</t>
+          <t>P50</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.02</v>
+        <v>0.75</v>
       </c>
       <c r="F23" t="n">
-        <v>1.188</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="24">
@@ -5156,23 +5156,23 @@
         <v>4</v>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P47</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.58</v>
+        <v>1.76</v>
       </c>
       <c r="F24" t="n">
-        <v>0.732</v>
+        <v>1.896</v>
       </c>
     </row>
     <row r="25">
@@ -5180,23 +5180,23 @@
         <v>4</v>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>P50</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.75</v>
+        <v>0.44</v>
       </c>
       <c r="F25" t="n">
-        <v>0.894</v>
+        <v>0.6799999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -5208,19 +5208,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.13</v>
+        <v>0.45</v>
       </c>
       <c r="F26" t="n">
-        <v>1.286</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="27">
@@ -5232,19 +5232,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.62</v>
+        <v>1.31</v>
       </c>
       <c r="F27" t="n">
-        <v>2.816</v>
+        <v>1.438</v>
       </c>
     </row>
     <row r="28">
@@ -5256,19 +5256,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>P30</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
       <c r="F28" t="n">
-        <v>1.174</v>
+        <v>0.8999999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -5280,19 +5280,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>P44</t>
+          <t>P38</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="F29" t="n">
-        <v>0.862</v>
+        <v>1.266</v>
       </c>
     </row>
     <row r="30">
@@ -5304,19 +5304,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>P45</t>
+          <t>P55</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.88</v>
+        <v>0.45</v>
       </c>
       <c r="F30" t="n">
-        <v>1.992</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="31">
@@ -5573,14 +5573,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="F41" t="n">
-        <v>0.866</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="42">
@@ -5597,14 +5597,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.49</v>
+        <v>0.38</v>
       </c>
       <c r="F42" t="n">
-        <v>0.75</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="43">
@@ -5669,14 +5669,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>P46</t>
+          <t>P51</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="F45" t="n">
-        <v>0.55</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="46">
@@ -5741,14 +5741,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.26</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>0.352</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="49">
@@ -5765,14 +5765,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6659999999999999</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="50">
@@ -5789,14 +5789,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.64</v>
+        <v>0.39</v>
       </c>
       <c r="F50" t="n">
-        <v>0.876</v>
+        <v>0.6659999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -5813,14 +5813,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="F51" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="52">
@@ -5837,14 +5837,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>P21</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.38</v>
+        <v>0.51</v>
       </c>
       <c r="F52" t="n">
-        <v>0.532</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="53">
@@ -5933,14 +5933,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>P49</t>
+          <t>P46</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.91</v>
+        <v>0.31</v>
       </c>
       <c r="F56" t="n">
-        <v>1.126</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="57">
@@ -5957,14 +5957,14 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>P51</t>
+          <t>P49</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="F57" t="n">
-        <v>0.448</v>
+        <v>1.126</v>
       </c>
     </row>
   </sheetData>
@@ -6022,19 +6022,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.46</v>
+        <v>1.76</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5680000000000001</v>
+        <v>1.896</v>
       </c>
     </row>
     <row r="3">
@@ -6046,19 +6046,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.74</v>
+        <v>0.44</v>
       </c>
       <c r="F3" t="n">
-        <v>0.864</v>
+        <v>0.6799999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -6070,19 +6070,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="F4" t="n">
-        <v>1.14</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="5">
@@ -6094,19 +6094,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.63</v>
+        <v>1.31</v>
       </c>
       <c r="F5" t="n">
-        <v>0.742</v>
+        <v>1.438</v>
       </c>
     </row>
     <row r="6">
@@ -6118,19 +6118,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>P25</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="F6" t="n">
-        <v>1.018</v>
+        <v>0.8999999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -6142,19 +6142,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>P26</t>
+          <t>P38</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.61</v>
+        <v>0.99</v>
       </c>
       <c r="F7" t="n">
-        <v>1.702</v>
+        <v>1.266</v>
       </c>
     </row>
     <row r="8">
@@ -6166,19 +6166,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>P28</t>
+          <t>P55</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.82</v>
+        <v>0.45</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9359999999999999</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="9">
@@ -6186,7 +6186,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -6195,14 +6195,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>P40</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6880000000000001</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="10">
@@ -6214,19 +6214,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P32</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>1.896</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="11">
@@ -6238,19 +6238,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P35</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.44</v>
+        <v>1.2</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6799999999999999</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -6262,19 +6262,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P36</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.45</v>
+        <v>1.13</v>
       </c>
       <c r="F12" t="n">
-        <v>0.618</v>
+        <v>1.278</v>
       </c>
     </row>
     <row r="13">
@@ -6286,19 +6286,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P40</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.31</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.438</v>
+        <v>0.6880000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -6310,19 +6310,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>P27</t>
+          <t>P42</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.7</v>
+        <v>1.07</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8999999999999999</v>
+        <v>1.226</v>
       </c>
     </row>
     <row r="15">
@@ -6334,19 +6334,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>P38</t>
+          <t>P43</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="F15" t="n">
-        <v>1.266</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="16">
@@ -6358,19 +6358,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P55</t>
+          <t>P47</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="F16" t="n">
-        <v>0.63</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="17">
@@ -6378,23 +6378,23 @@
         <v>5</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P50</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="F17" t="n">
-        <v>1.286</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="18">
@@ -6411,14 +6411,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.62</v>
+        <v>1.13</v>
       </c>
       <c r="F18" t="n">
-        <v>2.816</v>
+        <v>1.286</v>
       </c>
     </row>
     <row r="19">
@@ -6435,14 +6435,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>P30</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.05</v>
+        <v>2.62</v>
       </c>
       <c r="F19" t="n">
-        <v>1.174</v>
+        <v>2.816</v>
       </c>
     </row>
     <row r="20">
@@ -6459,14 +6459,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P44</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.75</v>
+        <v>1.05</v>
       </c>
       <c r="F20" t="n">
-        <v>0.862</v>
+        <v>1.174</v>
       </c>
     </row>
     <row r="21">
@@ -6483,14 +6483,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>P45</t>
+          <t>P44</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.88</v>
+        <v>0.75</v>
       </c>
       <c r="F21" t="n">
-        <v>1.992</v>
+        <v>0.862</v>
       </c>
     </row>
     <row r="22">
@@ -6498,23 +6498,23 @@
         <v>5</v>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P45</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.44</v>
+        <v>1.88</v>
       </c>
       <c r="F22" t="n">
-        <v>0.616</v>
+        <v>1.992</v>
       </c>
     </row>
     <row r="23">
@@ -6531,14 +6531,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.34</v>
+        <v>0.44</v>
       </c>
       <c r="F23" t="n">
-        <v>0.556</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="24">
@@ -6555,14 +6555,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="F24" t="n">
-        <v>0.514</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="25">
@@ -6579,14 +6579,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.91</v>
+        <v>0.33</v>
       </c>
       <c r="F25" t="n">
-        <v>1.082</v>
+        <v>0.514</v>
       </c>
     </row>
     <row r="26">
@@ -6603,14 +6603,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>P23</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.53</v>
+        <v>0.91</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7060000000000001</v>
+        <v>1.082</v>
       </c>
     </row>
     <row r="27">
@@ -6627,14 +6627,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>P29</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="F27" t="n">
-        <v>0.706</v>
+        <v>0.7060000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -6651,14 +6651,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>P34</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="F28" t="n">
-        <v>0.634</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="29">
@@ -6675,14 +6675,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>P37</t>
+          <t>P34</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="F29" t="n">
-        <v>0.78</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="30">
@@ -6699,14 +6699,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>P48</t>
+          <t>P37</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.39</v>
+        <v>0.58</v>
       </c>
       <c r="F30" t="n">
-        <v>0.526</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="31">
@@ -6723,14 +6723,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>P54</t>
+          <t>P48</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="F31" t="n">
-        <v>0.668</v>
+        <v>0.526</v>
       </c>
     </row>
     <row r="32">
@@ -6738,23 +6738,23 @@
         <v>5</v>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P54</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>0.644</v>
+        <v>0.668</v>
       </c>
     </row>
     <row r="33">
@@ -6771,14 +6771,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="F33" t="n">
-        <v>0.544</v>
+        <v>0.5680000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -6795,14 +6795,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>P32</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="F34" t="n">
-        <v>0.748</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="35">
@@ -6819,14 +6819,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>P35</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.2</v>
+        <v>0.74</v>
       </c>
       <c r="F35" t="n">
-        <v>1.4</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="36">
@@ -6843,14 +6843,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>P36</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>1.278</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="37">
@@ -6867,14 +6867,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>P42</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.07</v>
+        <v>0.63</v>
       </c>
       <c r="F37" t="n">
-        <v>1.226</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="38">
@@ -6891,14 +6891,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>P43</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="F38" t="n">
-        <v>1.188</v>
+        <v>1.018</v>
       </c>
     </row>
     <row r="39">
@@ -6915,14 +6915,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>P47</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.58</v>
+        <v>1.61</v>
       </c>
       <c r="F39" t="n">
-        <v>0.732</v>
+        <v>1.702</v>
       </c>
     </row>
     <row r="40">
@@ -6939,14 +6939,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>P50</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="F40" t="n">
-        <v>0.894</v>
+        <v>0.9359999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -6963,14 +6963,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6659999999999999</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="42">
@@ -6987,14 +6987,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
       <c r="F42" t="n">
-        <v>0.75</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="43">
@@ -7011,14 +7011,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.64</v>
+        <v>0.49</v>
       </c>
       <c r="F43" t="n">
-        <v>0.876</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="44">
@@ -7035,14 +7035,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>P33</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="F44" t="n">
-        <v>0.52</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="45">
@@ -7059,14 +7059,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>P39</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="46">
@@ -7083,14 +7083,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>P46</t>
+          <t>P33</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="F46" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="47">
@@ -7107,14 +7107,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>P49</t>
+          <t>P46</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.91</v>
+        <v>0.31</v>
       </c>
       <c r="F47" t="n">
-        <v>1.126</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="48">
@@ -7131,14 +7131,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>P51</t>
+          <t>P49</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="F48" t="n">
-        <v>0.448</v>
+        <v>1.126</v>
       </c>
     </row>
     <row r="49">
@@ -7179,14 +7179,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="F50" t="n">
-        <v>0.866</v>
+        <v>0.6659999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -7203,14 +7203,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.26</v>
+        <v>0.51</v>
       </c>
       <c r="F51" t="n">
-        <v>0.352</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="52">
@@ -7227,14 +7227,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="F52" t="n">
-        <v>0.71</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="53">
@@ -7251,14 +7251,14 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>P21</t>
+          <t>P31</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.38</v>
+        <v>0.61</v>
       </c>
       <c r="F53" t="n">
-        <v>0.532</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="54">
@@ -7275,14 +7275,14 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>P39</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.49</v>
+        <v>0.3</v>
       </c>
       <c r="F54" t="n">
-        <v>0.606</v>
+        <v>0.5720000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -7299,14 +7299,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>P31</t>
+          <t>P41</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.61</v>
+        <v>1.47</v>
       </c>
       <c r="F55" t="n">
-        <v>0.706</v>
+        <v>1.718</v>
       </c>
     </row>
     <row r="56">
@@ -7323,14 +7323,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>P41</t>
+          <t>P51</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.47</v>
+        <v>0.2</v>
       </c>
       <c r="F56" t="n">
-        <v>1.718</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="57">
@@ -7412,19 +7412,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.76</v>
+        <v>0.36</v>
       </c>
       <c r="F2" t="n">
-        <v>1.896</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="3">
@@ -7436,19 +7436,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P32</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="4">
@@ -7460,19 +7460,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P35</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.45</v>
+        <v>1.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.618</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="5">
@@ -7484,19 +7484,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P36</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="F5" t="n">
-        <v>1.438</v>
+        <v>1.278</v>
       </c>
     </row>
     <row r="6">
@@ -7508,19 +7508,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>P27</t>
+          <t>P40</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8999999999999999</v>
+        <v>0.6880000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -7532,19 +7532,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>P38</t>
+          <t>P42</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.99</v>
+        <v>1.07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.266</v>
+        <v>1.226</v>
       </c>
     </row>
     <row r="8">
@@ -7556,19 +7556,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>P55</t>
+          <t>P43</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.45</v>
+        <v>1.02</v>
       </c>
       <c r="F8" t="n">
-        <v>0.63</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="9">
@@ -7576,7 +7576,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -7585,14 +7585,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P47</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.46</v>
+        <v>0.58</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5680000000000001</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="10">
@@ -7600,7 +7600,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -7609,14 +7609,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P50</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.52</v>
+        <v>0.75</v>
       </c>
       <c r="F10" t="n">
-        <v>0.644</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="11">
@@ -7628,19 +7628,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.74</v>
+        <v>1.13</v>
       </c>
       <c r="F11" t="n">
-        <v>0.864</v>
+        <v>1.286</v>
       </c>
     </row>
     <row r="12">
@@ -7652,19 +7652,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.63</v>
+        <v>2.62</v>
       </c>
       <c r="F12" t="n">
-        <v>0.742</v>
+        <v>2.816</v>
       </c>
     </row>
     <row r="13">
@@ -7676,19 +7676,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>P25</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.89</v>
+        <v>1.05</v>
       </c>
       <c r="F13" t="n">
-        <v>1.018</v>
+        <v>1.174</v>
       </c>
     </row>
     <row r="14">
@@ -7700,19 +7700,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>P26</t>
+          <t>P44</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.61</v>
+        <v>0.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1.702</v>
+        <v>0.862</v>
       </c>
     </row>
     <row r="15">
@@ -7724,19 +7724,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>P28</t>
+          <t>P45</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.82</v>
+        <v>1.88</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9359999999999999</v>
+        <v>1.992</v>
       </c>
     </row>
     <row r="16">
@@ -7744,7 +7744,7 @@
         <v>6</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -7753,14 +7753,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P35</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.2</v>
+        <v>0.46</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4</v>
+        <v>0.5680000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -7772,19 +7772,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.13</v>
+        <v>0.52</v>
       </c>
       <c r="F17" t="n">
-        <v>1.286</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="18">
@@ -7796,19 +7796,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.62</v>
+        <v>0.74</v>
       </c>
       <c r="F18" t="n">
-        <v>2.816</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="19">
@@ -7820,19 +7820,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>P30</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1.174</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="20">
@@ -7844,19 +7844,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P44</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="F20" t="n">
-        <v>0.862</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="21">
@@ -7868,19 +7868,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>P45</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.88</v>
+        <v>0.89</v>
       </c>
       <c r="F21" t="n">
-        <v>1.992</v>
+        <v>1.018</v>
       </c>
     </row>
     <row r="22">
@@ -7888,23 +7888,23 @@
         <v>6</v>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.44</v>
+        <v>1.61</v>
       </c>
       <c r="F22" t="n">
-        <v>0.616</v>
+        <v>1.702</v>
       </c>
     </row>
     <row r="23">
@@ -7912,23 +7912,23 @@
         <v>6</v>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.34</v>
+        <v>0.82</v>
       </c>
       <c r="F23" t="n">
-        <v>0.556</v>
+        <v>0.9359999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -7940,19 +7940,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.33</v>
+        <v>1.76</v>
       </c>
       <c r="F24" t="n">
-        <v>0.514</v>
+        <v>1.896</v>
       </c>
     </row>
     <row r="25">
@@ -7964,19 +7964,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.91</v>
+        <v>0.44</v>
       </c>
       <c r="F25" t="n">
-        <v>1.082</v>
+        <v>0.6799999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -7988,19 +7988,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>P23</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7060000000000001</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="27">
@@ -8012,19 +8012,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>P29</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.57</v>
+        <v>1.31</v>
       </c>
       <c r="F27" t="n">
-        <v>0.706</v>
+        <v>1.438</v>
       </c>
     </row>
     <row r="28">
@@ -8036,19 +8036,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>P34</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="F28" t="n">
-        <v>0.634</v>
+        <v>0.8999999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -8060,19 +8060,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>P37</t>
+          <t>P38</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.58</v>
+        <v>0.99</v>
       </c>
       <c r="F29" t="n">
-        <v>0.78</v>
+        <v>1.266</v>
       </c>
     </row>
     <row r="30">
@@ -8084,19 +8084,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>P48</t>
+          <t>P55</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="F30" t="n">
-        <v>0.526</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="31">
@@ -8104,7 +8104,7 @@
         <v>6</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -8113,14 +8113,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>P54</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="F31" t="n">
-        <v>0.668</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="32">
@@ -8132,19 +8132,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="F32" t="n">
-        <v>0.544</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="33">
@@ -8156,19 +8156,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="F33" t="n">
-        <v>1.14</v>
+        <v>0.514</v>
       </c>
     </row>
     <row r="34">
@@ -8180,19 +8180,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>P32</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="F34" t="n">
-        <v>0.748</v>
+        <v>1.082</v>
       </c>
     </row>
     <row r="35">
@@ -8204,19 +8204,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>P36</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.13</v>
+        <v>0.53</v>
       </c>
       <c r="F35" t="n">
-        <v>1.278</v>
+        <v>0.7060000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -8228,19 +8228,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>P40</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6880000000000001</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="37">
@@ -8252,19 +8252,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>P42</t>
+          <t>P34</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.07</v>
+        <v>0.47</v>
       </c>
       <c r="F37" t="n">
-        <v>1.226</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="38">
@@ -8276,19 +8276,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>P43</t>
+          <t>P37</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.02</v>
+        <v>0.58</v>
       </c>
       <c r="F38" t="n">
-        <v>1.188</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="39">
@@ -8300,19 +8300,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>P47</t>
+          <t>P48</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.58</v>
+        <v>0.39</v>
       </c>
       <c r="F39" t="n">
-        <v>0.732</v>
+        <v>0.526</v>
       </c>
     </row>
     <row r="40">
@@ -8324,19 +8324,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>P50</t>
+          <t>P54</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>0.894</v>
+        <v>0.668</v>
       </c>
     </row>
     <row r="41">
@@ -8353,14 +8353,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6659999999999999</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="42">
@@ -8377,14 +8377,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="F42" t="n">
-        <v>0.75</v>
+        <v>0.6659999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -8401,14 +8401,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.64</v>
+        <v>0.49</v>
       </c>
       <c r="F43" t="n">
-        <v>0.876</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="44">
@@ -8425,14 +8425,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.51</v>
+        <v>0.64</v>
       </c>
       <c r="F44" t="n">
-        <v>0.71</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="45">
@@ -8449,14 +8449,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>P21</t>
+          <t>P33</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="F45" t="n">
-        <v>0.532</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="46">
@@ -8473,14 +8473,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>P33</t>
+          <t>P39</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="F46" t="n">
-        <v>0.52</v>
+        <v>0.5720000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -8497,14 +8497,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>P39</t>
+          <t>P46</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="48">
@@ -8521,14 +8521,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>P46</t>
+          <t>P51</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="F48" t="n">
-        <v>0.55</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="49">
@@ -8545,14 +8545,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>P51</t>
+          <t>P53</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.2</v>
+        <v>0.51</v>
       </c>
       <c r="F49" t="n">
-        <v>0.448</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="50">
@@ -8560,7 +8560,7 @@
         <v>6</v>
       </c>
       <c r="B50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -8569,14 +8569,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>P53</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="F50" t="n">
-        <v>0.742</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="51">
@@ -8593,14 +8593,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.51</v>
       </c>
       <c r="F51" t="n">
-        <v>0.866</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="52">
@@ -8617,14 +8617,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="F52" t="n">
-        <v>0.352</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="53">
